--- a/TASTI_SYNTHETIC/Pno7KP_Prefix.xlsx
+++ b/TASTI_SYNTHETIC/Pno7KP_Prefix.xlsx
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>60E60</t>
+          <t>25P91</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,19 +455,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>49F77</t>
+          <t>76B23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Body Parts</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>60Z39</t>
+          <t>49H49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,55 +479,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>49A63</t>
+          <t>38G78</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Brake Parts</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>33U26</t>
+          <t>88J19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>88J19</t>
+          <t>11S72</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39A71</t>
+          <t>93V13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brake Parts</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>33H94</t>
+          <t>66A12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,84 +539,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>71V60</t>
+          <t>66U36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>89L21</t>
+          <t>85P44</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Suspension</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>38B79</t>
+          <t>37N35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>71J22</t>
+          <t>43K35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Body Parts</t>
+          <t>Brake Parts</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23A43</t>
+          <t>84N83</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Body Parts</t>
+          <t>Electrical</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13X66</t>
+          <t>44T63</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Suspension</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52N10</t>
+          <t>70Z18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
